--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_coal_related_energy.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-2.14</v>
+        <v>-1.91</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.374</v>
+        <v>0.436</v>
       </c>
       <c r="V2">
-        <v>0.07123809523809524</v>
+        <v>0.1188010899182561</v>
       </c>
       <c r="W2">
-        <v>-0.1465753424657534</v>
+        <v>-0.137410071942446</v>
       </c>
       <c r="X2">
-        <v>0.2281696652205924</v>
+        <v>0.540313181428292</v>
       </c>
       <c r="Y2">
-        <v>-0.3747450076863458</v>
+        <v>-0.677723253370738</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.09595905746881329</v>
+        <v>-0.08754455860767456</v>
       </c>
       <c r="AB2">
-        <v>0.1447751944194309</v>
+        <v>0.2735712758582731</v>
       </c>
       <c r="AC2">
-        <v>-0.2407342518882442</v>
+        <v>-0.3611158344659477</v>
       </c>
       <c r="AD2">
-        <v>5.55</v>
+        <v>5.73</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.55</v>
+        <v>5.73</v>
       </c>
       <c r="AG2">
-        <v>5.176</v>
+        <v>5.294</v>
       </c>
       <c r="AH2">
-        <v>0.5138888888888888</v>
+        <v>0.6095744680851064</v>
       </c>
       <c r="AI2">
-        <v>0.2853470437017995</v>
+        <v>0.3059263214095035</v>
       </c>
       <c r="AJ2">
-        <v>0.4964511797429503</v>
+        <v>0.5905845604640786</v>
       </c>
       <c r="AK2">
-        <v>0.2713357097924093</v>
+        <v>0.2893844976495026</v>
       </c>
       <c r="AL2">
-        <v>0.524</v>
+        <v>0.605</v>
       </c>
       <c r="AM2">
-        <v>0.524</v>
+        <v>0.605</v>
       </c>
       <c r="AN2">
-        <v>-3.724832214765101</v>
+        <v>-4.006993006993008</v>
       </c>
       <c r="AO2">
-        <v>-3.435114503816794</v>
+        <v>-2.760330578512397</v>
       </c>
       <c r="AP2">
-        <v>-3.473825503355705</v>
+        <v>-3.702097902097903</v>
       </c>
       <c r="AQ2">
-        <v>-3.435114503816794</v>
+        <v>-2.760330578512397</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-2.14</v>
+        <v>-1.91</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +722,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.374</v>
+        <v>0.436</v>
       </c>
       <c r="V3">
-        <v>0.07123809523809524</v>
+        <v>0.1188010899182561</v>
       </c>
       <c r="W3">
-        <v>-0.1465753424657534</v>
+        <v>-0.137410071942446</v>
       </c>
       <c r="X3">
-        <v>0.2281696652205924</v>
+        <v>0.540313181428292</v>
       </c>
       <c r="Y3">
-        <v>-0.3747450076863458</v>
+        <v>-0.677723253370738</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.09595905746881329</v>
+        <v>-0.08754455860767456</v>
       </c>
       <c r="AB3">
-        <v>0.1447751944194309</v>
+        <v>0.2735712758582731</v>
       </c>
       <c r="AC3">
-        <v>-0.2407342518882442</v>
+        <v>-0.3611158344659477</v>
       </c>
       <c r="AD3">
-        <v>5.55</v>
+        <v>5.73</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.55</v>
+        <v>5.73</v>
       </c>
       <c r="AG3">
-        <v>5.176</v>
+        <v>5.294</v>
       </c>
       <c r="AH3">
-        <v>0.5138888888888888</v>
+        <v>0.6095744680851064</v>
       </c>
       <c r="AI3">
-        <v>0.2853470437017995</v>
+        <v>0.3059263214095035</v>
       </c>
       <c r="AJ3">
-        <v>0.4964511797429503</v>
+        <v>0.5905845604640786</v>
       </c>
       <c r="AK3">
-        <v>0.2713357097924093</v>
+        <v>0.2893844976495026</v>
       </c>
       <c r="AL3">
-        <v>0.524</v>
+        <v>0.605</v>
       </c>
       <c r="AM3">
-        <v>0.524</v>
+        <v>0.605</v>
       </c>
       <c r="AN3">
-        <v>-3.724832214765101</v>
+        <v>-4.006993006993008</v>
       </c>
       <c r="AO3">
-        <v>-3.435114503816794</v>
+        <v>-2.760330578512397</v>
       </c>
       <c r="AP3">
-        <v>-3.473825503355705</v>
+        <v>-3.702097902097903</v>
       </c>
       <c r="AQ3">
-        <v>-3.435114503816794</v>
+        <v>-2.760330578512397</v>
       </c>
     </row>
   </sheetData>
